--- a/1_network_estimation/1_data_cleaning/Data_clean/MCAS/Estados_US/Edos_USA_2019/WYOMING_2019.xlsx
+++ b/1_network_estimation/1_data_cleaning/Data_clean/MCAS/Estados_US/Edos_USA_2019/WYOMING_2019.xlsx
@@ -351,28 +351,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D288"/>
+  <dimension ref="A1:D282"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Estado de Origen</t>
+          <t>mx_state</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Municipio Origen</t>
+          <t>mx_municipality</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Número de Matrículas</t>
+          <t>n_matriculas</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Porcentaje de Matrículas</t>
+          <t>pct_matriculas</t>
         </is>
       </c>
     </row>
@@ -395,6 +395,11 @@
       </c>
     </row>
     <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
           <t>Jesús María</t>
@@ -408,6 +413,11 @@
       </c>
     </row>
     <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B4" t="inlineStr">
         <is>
           <t>Total</t>
@@ -439,6 +449,11 @@
       </c>
     </row>
     <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Baja California</t>
+        </is>
+      </c>
       <c r="B6" t="inlineStr">
         <is>
           <t>Tijuana</t>
@@ -452,6 +467,11 @@
       </c>
     </row>
     <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Baja California</t>
+        </is>
+      </c>
       <c r="B7" t="inlineStr">
         <is>
           <t>Total</t>
@@ -483,6 +503,11 @@
       </c>
     </row>
     <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B9" t="inlineStr">
         <is>
           <t>Cacahoatán</t>
@@ -496,6 +521,11 @@
       </c>
     </row>
     <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B10" t="inlineStr">
         <is>
           <t>Coapilla</t>
@@ -509,6 +539,11 @@
       </c>
     </row>
     <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B11" t="inlineStr">
         <is>
           <t>Frontera Comalapa</t>
@@ -522,9 +557,14 @@
       </c>
     </row>
     <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Mazapa de Madero</t>
+          <t>Mazapa De Madero</t>
         </is>
       </c>
       <c r="C12">
@@ -535,6 +575,11 @@
       </c>
     </row>
     <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B13" t="inlineStr">
         <is>
           <t>Tapachula</t>
@@ -548,6 +593,11 @@
       </c>
     </row>
     <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B14" t="inlineStr">
         <is>
           <t>Villa Comaltitlán</t>
@@ -561,6 +611,11 @@
       </c>
     </row>
     <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B15" t="inlineStr">
         <is>
           <t>Total</t>
@@ -592,6 +647,11 @@
       </c>
     </row>
     <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B17" t="inlineStr">
         <is>
           <t>Ascensión</t>
@@ -605,6 +665,11 @@
       </c>
     </row>
     <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B18" t="inlineStr">
         <is>
           <t>Balleza</t>
@@ -618,6 +683,11 @@
       </c>
     </row>
     <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B19" t="inlineStr">
         <is>
           <t>Buenaventura</t>
@@ -631,6 +701,11 @@
       </c>
     </row>
     <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B20" t="inlineStr">
         <is>
           <t>Camargo</t>
@@ -644,6 +719,11 @@
       </c>
     </row>
     <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B21" t="inlineStr">
         <is>
           <t>Carichí</t>
@@ -657,6 +737,11 @@
       </c>
     </row>
     <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B22" t="inlineStr">
         <is>
           <t>Chihuahua</t>
@@ -670,6 +755,11 @@
       </c>
     </row>
     <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B23" t="inlineStr">
         <is>
           <t>Cuauhtémoc</t>
@@ -683,6 +773,11 @@
       </c>
     </row>
     <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B24" t="inlineStr">
         <is>
           <t>Delicias</t>
@@ -696,6 +791,11 @@
       </c>
     </row>
     <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B25" t="inlineStr">
         <is>
           <t>Gómez Farías</t>
@@ -709,6 +809,11 @@
       </c>
     </row>
     <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B26" t="inlineStr">
         <is>
           <t>Guachochi</t>
@@ -722,6 +827,11 @@
       </c>
     </row>
     <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B27" t="inlineStr">
         <is>
           <t>Guerrero</t>
@@ -735,9 +845,14 @@
       </c>
     </row>
     <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Hidalgo del Parral</t>
+          <t>Hidalgo Del Parral</t>
         </is>
       </c>
       <c r="C28">
@@ -748,6 +863,11 @@
       </c>
     </row>
     <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B29" t="inlineStr">
         <is>
           <t>Ignacio Zaragoza</t>
@@ -761,6 +881,11 @@
       </c>
     </row>
     <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B30" t="inlineStr">
         <is>
           <t>Juárez</t>
@@ -774,6 +899,11 @@
       </c>
     </row>
     <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B31" t="inlineStr">
         <is>
           <t>López</t>
@@ -787,6 +917,11 @@
       </c>
     </row>
     <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B32" t="inlineStr">
         <is>
           <t>Madera</t>
@@ -800,6 +935,11 @@
       </c>
     </row>
     <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B33" t="inlineStr">
         <is>
           <t>Matachí</t>
@@ -813,6 +953,11 @@
       </c>
     </row>
     <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B34" t="inlineStr">
         <is>
           <t>Namiquipa</t>
@@ -826,6 +971,11 @@
       </c>
     </row>
     <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B35" t="inlineStr">
         <is>
           <t>Nuevo Casas Grandes</t>
@@ -839,6 +989,11 @@
       </c>
     </row>
     <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B36" t="inlineStr">
         <is>
           <t>Ocampo</t>
@@ -852,6 +1007,11 @@
       </c>
     </row>
     <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B37" t="inlineStr">
         <is>
           <t>Rosario</t>
@@ -865,9 +1025,14 @@
       </c>
     </row>
     <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>San Francisco de Borja</t>
+          <t>San Francisco De Borja</t>
         </is>
       </c>
       <c r="C38">
@@ -878,6 +1043,11 @@
       </c>
     </row>
     <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B39" t="inlineStr">
         <is>
           <t>Saucillo</t>
@@ -891,9 +1061,14 @@
       </c>
     </row>
     <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Valle de Zaragoza</t>
+          <t>Valle De Zaragoza</t>
         </is>
       </c>
       <c r="C40">
@@ -904,6 +1079,11 @@
       </c>
     </row>
     <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B41" t="inlineStr">
         <is>
           <t>Total</t>
@@ -935,6 +1115,11 @@
       </c>
     </row>
     <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B43" t="inlineStr">
         <is>
           <t>Piedras Negras</t>
@@ -948,6 +1133,11 @@
       </c>
     </row>
     <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B44" t="inlineStr">
         <is>
           <t>Torreón</t>
@@ -961,6 +1151,11 @@
       </c>
     </row>
     <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B45" t="inlineStr">
         <is>
           <t>Viesca</t>
@@ -974,6 +1169,11 @@
       </c>
     </row>
     <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B46" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1005,6 +1205,11 @@
       </c>
     </row>
     <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Colima</t>
+        </is>
+      </c>
       <c r="B48" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1020,7 +1225,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Ciudad de México</t>
+          <t>Ciudad De México</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1036,6 +1241,11 @@
       </c>
     </row>
     <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B50" t="inlineStr">
         <is>
           <t>Azcapotzalco</t>
@@ -1049,6 +1259,11 @@
       </c>
     </row>
     <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B51" t="inlineStr">
         <is>
           <t>Benito Juárez</t>
@@ -1062,6 +1277,11 @@
       </c>
     </row>
     <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B52" t="inlineStr">
         <is>
           <t>Coyoacán</t>
@@ -1075,6 +1295,11 @@
       </c>
     </row>
     <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B53" t="inlineStr">
         <is>
           <t>Cuauhtémoc</t>
@@ -1088,6 +1313,11 @@
       </c>
     </row>
     <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B54" t="inlineStr">
         <is>
           <t>Gustavo A. Madero</t>
@@ -1101,6 +1331,11 @@
       </c>
     </row>
     <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B55" t="inlineStr">
         <is>
           <t>Iztacalco</t>
@@ -1114,6 +1349,11 @@
       </c>
     </row>
     <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B56" t="inlineStr">
         <is>
           <t>Iztapalapa</t>
@@ -1127,6 +1367,11 @@
       </c>
     </row>
     <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B57" t="inlineStr">
         <is>
           <t>Miguel Hidalgo</t>
@@ -1140,6 +1385,11 @@
       </c>
     </row>
     <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B58" t="inlineStr">
         <is>
           <t>Venustiano Carranza</t>
@@ -1153,6 +1403,11 @@
       </c>
     </row>
     <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B59" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1173,7 +1428,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Coneto de Comonfort</t>
+          <t>Coneto De Comonfort</t>
         </is>
       </c>
       <c r="C60">
@@ -1184,6 +1439,11 @@
       </c>
     </row>
     <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B61" t="inlineStr">
         <is>
           <t>Cuencamé</t>
@@ -1197,6 +1457,11 @@
       </c>
     </row>
     <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B62" t="inlineStr">
         <is>
           <t>Durango</t>
@@ -1210,6 +1475,11 @@
       </c>
     </row>
     <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B63" t="inlineStr">
         <is>
           <t>Guadalupe Victoria</t>
@@ -1223,6 +1493,11 @@
       </c>
     </row>
     <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B64" t="inlineStr">
         <is>
           <t>Lerdo</t>
@@ -1236,9 +1511,14 @@
       </c>
     </row>
     <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Nombre de Dios</t>
+          <t>Nombre De Dios</t>
         </is>
       </c>
       <c r="C65">
@@ -1249,6 +1529,11 @@
       </c>
     </row>
     <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B66" t="inlineStr">
         <is>
           <t>Ocampo</t>
@@ -1262,6 +1547,11 @@
       </c>
     </row>
     <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B67" t="inlineStr">
         <is>
           <t>Rodeo</t>
@@ -1275,6 +1565,11 @@
       </c>
     </row>
     <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B68" t="inlineStr">
         <is>
           <t>San Bernardo</t>
@@ -1288,6 +1583,11 @@
       </c>
     </row>
     <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B69" t="inlineStr">
         <is>
           <t>Santa Clara</t>
@@ -1301,6 +1601,11 @@
       </c>
     </row>
     <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B70" t="inlineStr">
         <is>
           <t>Vicente Guerrero</t>
@@ -1314,6 +1619,11 @@
       </c>
     </row>
     <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B71" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1329,7 +1639,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Estado de México</t>
+          <t>Estado De México</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -1345,9 +1655,14 @@
       </c>
     </row>
     <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Ecatepec de Morelos</t>
+          <t>Ecatepec De Morelos</t>
         </is>
       </c>
       <c r="C73">
@@ -1358,6 +1673,11 @@
       </c>
     </row>
     <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B74" t="inlineStr">
         <is>
           <t>Nezahualcóyotl</t>
@@ -1371,6 +1691,11 @@
       </c>
     </row>
     <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B75" t="inlineStr">
         <is>
           <t>Otumba</t>
@@ -1384,6 +1709,11 @@
       </c>
     </row>
     <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B76" t="inlineStr">
         <is>
           <t>Temascaltepec</t>
@@ -1397,9 +1727,14 @@
       </c>
     </row>
     <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Tlalnepantla de Baz</t>
+          <t>Tlalnepantla De Baz</t>
         </is>
       </c>
       <c r="C77">
@@ -1410,6 +1745,11 @@
       </c>
     </row>
     <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B78" t="inlineStr">
         <is>
           <t>Tlatlaya</t>
@@ -1423,6 +1763,11 @@
       </c>
     </row>
     <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B79" t="inlineStr">
         <is>
           <t>Toluca</t>
@@ -1436,6 +1781,11 @@
       </c>
     </row>
     <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B80" t="inlineStr">
         <is>
           <t>Xalatlaco</t>
@@ -1449,6 +1799,11 @@
       </c>
     </row>
     <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B81" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1480,6 +1835,11 @@
       </c>
     </row>
     <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B83" t="inlineStr">
         <is>
           <t>Doctor Mora</t>
@@ -1493,6 +1853,11 @@
       </c>
     </row>
     <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B84" t="inlineStr">
         <is>
           <t>Guanajuato</t>
@@ -1506,6 +1871,11 @@
       </c>
     </row>
     <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B85" t="inlineStr">
         <is>
           <t>Salamanca</t>
@@ -1519,9 +1889,14 @@
       </c>
     </row>
     <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Santa Cruz de Juventino Rosas</t>
+          <t>Santa Cruz De Juventino Rosas</t>
         </is>
       </c>
       <c r="C86">
@@ -1532,9 +1907,14 @@
       </c>
     </row>
     <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Silao de la Victoria</t>
+          <t>Silao De La Victoria</t>
         </is>
       </c>
       <c r="C87">
@@ -1545,6 +1925,11 @@
       </c>
     </row>
     <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B88" t="inlineStr">
         <is>
           <t>Yuriria</t>
@@ -1558,6 +1943,11 @@
       </c>
     </row>
     <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B89" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1578,7 +1968,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Acapulco de Juárez</t>
+          <t>Acapulco De Juárez</t>
         </is>
       </c>
       <c r="C90">
@@ -1589,9 +1979,14 @@
       </c>
     </row>
     <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Chilpancingo de los Bravo</t>
+          <t>Chilpancingo De Los Bravo</t>
         </is>
       </c>
       <c r="C91">
@@ -1602,9 +1997,14 @@
       </c>
     </row>
     <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Coyuca de Catalán</t>
+          <t>Coyuca De Catalán</t>
         </is>
       </c>
       <c r="C92">
@@ -1615,9 +2015,14 @@
       </c>
     </row>
     <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Huitzuco de los Figueroa</t>
+          <t>Huitzuco De Los Figueroa</t>
         </is>
       </c>
       <c r="C93">
@@ -1628,6 +2033,11 @@
       </c>
     </row>
     <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B94" t="inlineStr">
         <is>
           <t>Juan R. Escudero</t>
@@ -1641,6 +2051,11 @@
       </c>
     </row>
     <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B95" t="inlineStr">
         <is>
           <t>Teloloapan</t>
@@ -1654,6 +2069,11 @@
       </c>
     </row>
     <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B96" t="inlineStr">
         <is>
           <t>Tlalchapa</t>
@@ -1667,6 +2087,11 @@
       </c>
     </row>
     <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B97" t="inlineStr">
         <is>
           <t>Tlapehuala</t>
@@ -1680,6 +2105,11 @@
       </c>
     </row>
     <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B98" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1700,7 +2130,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Cuautepec de Hinojosa</t>
+          <t>Cuautepec De Hinojosa</t>
         </is>
       </c>
       <c r="C99">
@@ -1711,6 +2141,11 @@
       </c>
     </row>
     <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B100" t="inlineStr">
         <is>
           <t>El Arenal</t>
@@ -1724,6 +2159,11 @@
       </c>
     </row>
     <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B101" t="inlineStr">
         <is>
           <t>Huichapan</t>
@@ -1737,9 +2177,14 @@
       </c>
     </row>
     <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Mixquiahuala de Juárez</t>
+          <t>Mixquiahuala De Juárez</t>
         </is>
       </c>
       <c r="C102">
@@ -1750,6 +2195,11 @@
       </c>
     </row>
     <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B103" t="inlineStr">
         <is>
           <t>Tlahuiltepa</t>
@@ -1763,9 +2213,14 @@
       </c>
     </row>
     <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Tulancingo de Bravo</t>
+          <t>Tulancingo De Bravo</t>
         </is>
       </c>
       <c r="C104">
@@ -1776,6 +2231,11 @@
       </c>
     </row>
     <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B105" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1807,9 +2267,14 @@
       </c>
     </row>
     <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Autlán de Navarro</t>
+          <t>Autlán De Navarro</t>
         </is>
       </c>
       <c r="C107">
@@ -1820,6 +2285,11 @@
       </c>
     </row>
     <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B108" t="inlineStr">
         <is>
           <t>Ayotlán</t>
@@ -1833,6 +2303,11 @@
       </c>
     </row>
     <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B109" t="inlineStr">
         <is>
           <t>Ayutla</t>
@@ -1846,6 +2321,11 @@
       </c>
     </row>
     <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B110" t="inlineStr">
         <is>
           <t>Cocula</t>
@@ -1859,6 +2339,11 @@
       </c>
     </row>
     <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B111" t="inlineStr">
         <is>
           <t>El Grullo</t>
@@ -1872,9 +2357,14 @@
       </c>
     </row>
     <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Encarnación de Díaz</t>
+          <t>Encarnación De Díaz</t>
         </is>
       </c>
       <c r="C112">
@@ -1885,6 +2375,11 @@
       </c>
     </row>
     <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B113" t="inlineStr">
         <is>
           <t>Guadalajara</t>
@@ -1898,6 +2393,11 @@
       </c>
     </row>
     <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B114" t="inlineStr">
         <is>
           <t>Jamay</t>
@@ -1911,6 +2411,11 @@
       </c>
     </row>
     <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B115" t="inlineStr">
         <is>
           <t>La Barca</t>
@@ -1924,9 +2429,14 @@
       </c>
     </row>
     <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Lagos de Moreno</t>
+          <t>Lagos De Moreno</t>
         </is>
       </c>
       <c r="C116">
@@ -1937,6 +2447,11 @@
       </c>
     </row>
     <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B117" t="inlineStr">
         <is>
           <t>Ocotlán</t>
@@ -1950,6 +2465,11 @@
       </c>
     </row>
     <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B118" t="inlineStr">
         <is>
           <t>Pihuamo</t>
@@ -1963,6 +2483,11 @@
       </c>
     </row>
     <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B119" t="inlineStr">
         <is>
           <t>Puerto Vallarta</t>
@@ -1976,9 +2501,14 @@
       </c>
     </row>
     <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>San Juan de los Lagos</t>
+          <t>San Juan De Los Lagos</t>
         </is>
       </c>
       <c r="C120">
@@ -1989,6 +2519,11 @@
       </c>
     </row>
     <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B121" t="inlineStr">
         <is>
           <t>San Julián</t>
@@ -2002,9 +2537,14 @@
       </c>
     </row>
     <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>San Miguel el Alto</t>
+          <t>San Miguel El Alto</t>
         </is>
       </c>
       <c r="C122">
@@ -2015,9 +2555,14 @@
       </c>
     </row>
     <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>San Sebastián del Oeste</t>
+          <t>San Sebastián Del Oeste</t>
         </is>
       </c>
       <c r="C123">
@@ -2028,6 +2573,11 @@
       </c>
     </row>
     <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B124" t="inlineStr">
         <is>
           <t>Tala</t>
@@ -2041,9 +2591,14 @@
       </c>
     </row>
     <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Tamazula de Gordiano</t>
+          <t>Tamazula De Gordiano</t>
         </is>
       </c>
       <c r="C125">
@@ -2054,6 +2609,11 @@
       </c>
     </row>
     <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B126" t="inlineStr">
         <is>
           <t>Tenamaxtlán</t>
@@ -2067,6 +2627,11 @@
       </c>
     </row>
     <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B127" t="inlineStr">
         <is>
           <t>Tequila</t>
@@ -2080,6 +2645,11 @@
       </c>
     </row>
     <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B128" t="inlineStr">
         <is>
           <t>San Pedro Tlaquepaque</t>
@@ -2093,6 +2663,11 @@
       </c>
     </row>
     <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B129" t="inlineStr">
         <is>
           <t>Tomatlán</t>
@@ -2106,9 +2681,14 @@
       </c>
     </row>
     <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Unión de Tula</t>
+          <t>Unión De Tula</t>
         </is>
       </c>
       <c r="C130">
@@ -2119,6 +2699,11 @@
       </c>
     </row>
     <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B131" t="inlineStr">
         <is>
           <t>Villa Purificación</t>
@@ -2132,6 +2717,11 @@
       </c>
     </row>
     <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B132" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2163,6 +2753,11 @@
       </c>
     </row>
     <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B134" t="inlineStr">
         <is>
           <t>Angamacutiro</t>
@@ -2176,6 +2771,11 @@
       </c>
     </row>
     <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B135" t="inlineStr">
         <is>
           <t>Carácuaro</t>
@@ -2189,6 +2789,11 @@
       </c>
     </row>
     <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B136" t="inlineStr">
         <is>
           <t>Charo</t>
@@ -2202,6 +2807,11 @@
       </c>
     </row>
     <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B137" t="inlineStr">
         <is>
           <t>Contepec</t>
@@ -2215,6 +2825,11 @@
       </c>
     </row>
     <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B138" t="inlineStr">
         <is>
           <t>Cotija</t>
@@ -2228,6 +2843,11 @@
       </c>
     </row>
     <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B139" t="inlineStr">
         <is>
           <t>Cuitzeo</t>
@@ -2241,6 +2861,11 @@
       </c>
     </row>
     <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B140" t="inlineStr">
         <is>
           <t>Hidalgo</t>
@@ -2254,6 +2879,11 @@
       </c>
     </row>
     <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B141" t="inlineStr">
         <is>
           <t>La Piedad</t>
@@ -2267,6 +2897,11 @@
       </c>
     </row>
     <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B142" t="inlineStr">
         <is>
           <t>Morelia</t>
@@ -2280,6 +2915,11 @@
       </c>
     </row>
     <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B143" t="inlineStr">
         <is>
           <t>Nocupétaro</t>
@@ -2293,6 +2933,11 @@
       </c>
     </row>
     <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B144" t="inlineStr">
         <is>
           <t>Queréndaro</t>
@@ -2306,6 +2951,11 @@
       </c>
     </row>
     <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B145" t="inlineStr">
         <is>
           <t>Salvador Escalante</t>
@@ -2319,6 +2969,11 @@
       </c>
     </row>
     <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B146" t="inlineStr">
         <is>
           <t>Tangancícuaro</t>
@@ -2332,6 +2987,11 @@
       </c>
     </row>
     <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B147" t="inlineStr">
         <is>
           <t>Tepalcatepec</t>
@@ -2345,6 +3005,11 @@
       </c>
     </row>
     <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B148" t="inlineStr">
         <is>
           <t>Tzitzio</t>
@@ -2358,6 +3023,11 @@
       </c>
     </row>
     <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B149" t="inlineStr">
         <is>
           <t>Yurécuaro</t>
@@ -2371,6 +3041,11 @@
       </c>
     </row>
     <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B150" t="inlineStr">
         <is>
           <t>Zacapu</t>
@@ -2384,6 +3059,11 @@
       </c>
     </row>
     <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B151" t="inlineStr">
         <is>
           <t>Zamora</t>
@@ -2397,6 +3077,11 @@
       </c>
     </row>
     <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B152" t="inlineStr">
         <is>
           <t>Zinapécuaro</t>
@@ -2410,6 +3095,11 @@
       </c>
     </row>
     <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B153" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2441,9 +3131,14 @@
       </c>
     </row>
     <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Tetela del Volcán</t>
+          <t>Tetela Del Volcán</t>
         </is>
       </c>
       <c r="C155">
@@ -2454,6 +3149,11 @@
       </c>
     </row>
     <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B156" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2485,6 +3185,11 @@
       </c>
     </row>
     <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B158" t="inlineStr">
         <is>
           <t>Ahuacatlán</t>
@@ -2498,9 +3203,14 @@
       </c>
     </row>
     <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Amatlán de Cañas</t>
+          <t>Amatlán De Cañas</t>
         </is>
       </c>
       <c r="C159">
@@ -2511,6 +3221,11 @@
       </c>
     </row>
     <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B160" t="inlineStr">
         <is>
           <t>Compostela</t>
@@ -2524,6 +3239,11 @@
       </c>
     </row>
     <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B161" t="inlineStr">
         <is>
           <t>La Yesca</t>
@@ -2537,9 +3257,14 @@
       </c>
     </row>
     <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Santa María del Oro</t>
+          <t>Santa María Del Oro</t>
         </is>
       </c>
       <c r="C162">
@@ -2550,6 +3275,11 @@
       </c>
     </row>
     <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B163" t="inlineStr">
         <is>
           <t>Santiago Ixcuintla</t>
@@ -2563,6 +3293,11 @@
       </c>
     </row>
     <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B164" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2594,6 +3329,11 @@
       </c>
     </row>
     <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B166" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2614,7 +3354,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Heroica Ciudad de Juchitán de Zaragoza</t>
+          <t>Heroica Ciudad De Juchitán De Zaragoza</t>
         </is>
       </c>
       <c r="C167">
@@ -2625,6 +3365,11 @@
       </c>
     </row>
     <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B168" t="inlineStr">
         <is>
           <t>Magdalena Teitipac</t>
@@ -2638,9 +3383,14 @@
       </c>
     </row>
     <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Ocotlán de Morelos</t>
+          <t>Ocotlán De Morelos</t>
         </is>
       </c>
       <c r="C169">
@@ -2651,9 +3401,14 @@
       </c>
     </row>
     <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Putla Villa de Guerrero</t>
+          <t>Putla Villa De Guerrero</t>
         </is>
       </c>
       <c r="C170">
@@ -2664,6 +3419,11 @@
       </c>
     </row>
     <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B171" t="inlineStr">
         <is>
           <t>San Juan Lachao</t>
@@ -2677,6 +3437,11 @@
       </c>
     </row>
     <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B172" t="inlineStr">
         <is>
           <t>San Miguel Quetzaltepec</t>
@@ -2690,6 +3455,11 @@
       </c>
     </row>
     <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B173" t="inlineStr">
         <is>
           <t>San Miguel Soyaltepec</t>
@@ -2703,6 +3473,11 @@
       </c>
     </row>
     <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B174" t="inlineStr">
         <is>
           <t>Santa Ana Zegache</t>
@@ -2716,6 +3491,11 @@
       </c>
     </row>
     <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B175" t="inlineStr">
         <is>
           <t>Santa María Jacatepec</t>
@@ -2729,6 +3509,11 @@
       </c>
     </row>
     <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B176" t="inlineStr">
         <is>
           <t>Santiago Amoltepec</t>
@@ -2742,6 +3527,11 @@
       </c>
     </row>
     <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B177" t="inlineStr">
         <is>
           <t>Santiago Juxtlahuaca</t>
@@ -2755,6 +3545,11 @@
       </c>
     </row>
     <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B178" t="inlineStr">
         <is>
           <t>Santiago Lachiguiri</t>
@@ -2768,6 +3563,11 @@
       </c>
     </row>
     <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B179" t="inlineStr">
         <is>
           <t>Santiago Pinotepa Nacional</t>
@@ -2781,6 +3581,11 @@
       </c>
     </row>
     <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B180" t="inlineStr">
         <is>
           <t>Santiago Yosondúa</t>
@@ -2794,9 +3599,14 @@
       </c>
     </row>
     <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Tlacolula de Matamoros</t>
+          <t>Tlacolula De Matamoros</t>
         </is>
       </c>
       <c r="C181">
@@ -2807,6 +3617,11 @@
       </c>
     </row>
     <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B182" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2838,6 +3653,11 @@
       </c>
     </row>
     <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B184" t="inlineStr">
         <is>
           <t>Coyomeapan</t>
@@ -2851,9 +3671,14 @@
       </c>
     </row>
     <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Cuayuca de Andrade</t>
+          <t>Cuayuca De Andrade</t>
         </is>
       </c>
       <c r="C185">
@@ -2864,6 +3689,11 @@
       </c>
     </row>
     <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B186" t="inlineStr">
         <is>
           <t>Epatlán</t>
@@ -2877,6 +3707,11 @@
       </c>
     </row>
     <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B187" t="inlineStr">
         <is>
           <t>Esperanza</t>
@@ -2890,6 +3725,11 @@
       </c>
     </row>
     <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B188" t="inlineStr">
         <is>
           <t>Ixtacamaxtitlán</t>
@@ -2903,6 +3743,11 @@
       </c>
     </row>
     <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B189" t="inlineStr">
         <is>
           <t>Jolalpan</t>
@@ -2916,6 +3761,11 @@
       </c>
     </row>
     <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B190" t="inlineStr">
         <is>
           <t>Puebla</t>
@@ -2929,6 +3779,11 @@
       </c>
     </row>
     <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B191" t="inlineStr">
         <is>
           <t>Quimixtlán</t>
@@ -2942,6 +3797,11 @@
       </c>
     </row>
     <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B192" t="inlineStr">
         <is>
           <t>Tepeaca</t>
@@ -2955,9 +3815,14 @@
       </c>
     </row>
     <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Tepexi de Rodríguez</t>
+          <t>Tepexi De Rodríguez</t>
         </is>
       </c>
       <c r="C193">
@@ -2968,6 +3833,11 @@
       </c>
     </row>
     <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B194" t="inlineStr">
         <is>
           <t>Teziutlán</t>
@@ -2981,6 +3851,11 @@
       </c>
     </row>
     <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B195" t="inlineStr">
         <is>
           <t>Tlaola</t>
@@ -2994,6 +3869,11 @@
       </c>
     </row>
     <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B196" t="inlineStr">
         <is>
           <t>Tlapacoya</t>
@@ -3007,6 +3887,11 @@
       </c>
     </row>
     <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B197" t="inlineStr">
         <is>
           <t>Xochitlán Todos Santos</t>
@@ -3020,6 +3905,11 @@
       </c>
     </row>
     <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B198" t="inlineStr">
         <is>
           <t>Zongozotla</t>
@@ -3033,6 +3923,11 @@
       </c>
     </row>
     <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B199" t="inlineStr">
         <is>
           <t>Total</t>
@@ -3053,7 +3948,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Amealco de Bonfil</t>
+          <t>Amealco De Bonfil</t>
         </is>
       </c>
       <c r="C200">
@@ -3064,6 +3959,11 @@
       </c>
     </row>
     <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B201" t="inlineStr">
         <is>
           <t>Huimilpan</t>
@@ -3077,9 +3977,14 @@
       </c>
     </row>
     <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Pinal de Amoles</t>
+          <t>Pinal De Amoles</t>
         </is>
       </c>
       <c r="C202">
@@ -3090,9 +3995,14 @@
       </c>
     </row>
     <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>San Juan del Río</t>
+          <t>San Juan Del Río</t>
         </is>
       </c>
       <c r="C203">
@@ -3103,6 +4013,11 @@
       </c>
     </row>
     <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B204" t="inlineStr">
         <is>
           <t>Total</t>
@@ -3134,6 +4049,11 @@
       </c>
     </row>
     <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B206" t="inlineStr">
         <is>
           <t>Ciudad Valles</t>
@@ -3147,6 +4067,11 @@
       </c>
     </row>
     <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B207" t="inlineStr">
         <is>
           <t>Matehuala</t>
@@ -3160,6 +4085,11 @@
       </c>
     </row>
     <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B208" t="inlineStr">
         <is>
           <t>Salinas</t>
@@ -3173,6 +4103,11 @@
       </c>
     </row>
     <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B209" t="inlineStr">
         <is>
           <t>San Luis Potosí</t>
@@ -3186,9 +4121,14 @@
       </c>
     </row>
     <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Santa María del Río</t>
+          <t>Santa María Del Río</t>
         </is>
       </c>
       <c r="C210">
@@ -3199,6 +4139,11 @@
       </c>
     </row>
     <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B211" t="inlineStr">
         <is>
           <t>Tampamolón Corona</t>
@@ -3212,9 +4157,14 @@
       </c>
     </row>
     <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Villa de Arista</t>
+          <t>Villa De Arista</t>
         </is>
       </c>
       <c r="C212">
@@ -3225,9 +4175,14 @@
       </c>
     </row>
     <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Villa de Ramos</t>
+          <t>Villa De Ramos</t>
         </is>
       </c>
       <c r="C213">
@@ -3238,6 +4193,11 @@
       </c>
     </row>
     <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B214" t="inlineStr">
         <is>
           <t>Total</t>
@@ -3269,6 +4229,11 @@
       </c>
     </row>
     <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B216" t="inlineStr">
         <is>
           <t>Choix</t>
@@ -3282,6 +4247,11 @@
       </c>
     </row>
     <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B217" t="inlineStr">
         <is>
           <t>Culiacán</t>
@@ -3295,6 +4265,11 @@
       </c>
     </row>
     <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B218" t="inlineStr">
         <is>
           <t>Elota</t>
@@ -3308,6 +4283,11 @@
       </c>
     </row>
     <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B219" t="inlineStr">
         <is>
           <t>Escuinapa</t>
@@ -3321,6 +4301,11 @@
       </c>
     </row>
     <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B220" t="inlineStr">
         <is>
           <t>Navolato</t>
@@ -3334,6 +4319,11 @@
       </c>
     </row>
     <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B221" t="inlineStr">
         <is>
           <t>Salvador Alvarado</t>
@@ -3347,6 +4337,11 @@
       </c>
     </row>
     <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B222" t="inlineStr">
         <is>
           <t>Total</t>
@@ -3378,6 +4373,11 @@
       </c>
     </row>
     <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B224" t="inlineStr">
         <is>
           <t>Baviácora</t>
@@ -3391,6 +4391,11 @@
       </c>
     </row>
     <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B225" t="inlineStr">
         <is>
           <t>Guaymas</t>
@@ -3404,6 +4409,11 @@
       </c>
     </row>
     <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B226" t="inlineStr">
         <is>
           <t>Hermosillo</t>
@@ -3417,6 +4427,11 @@
       </c>
     </row>
     <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B227" t="inlineStr">
         <is>
           <t>Nogales</t>
@@ -3430,6 +4445,11 @@
       </c>
     </row>
     <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B228" t="inlineStr">
         <is>
           <t>Sahuaripa</t>
@@ -3443,6 +4463,11 @@
       </c>
     </row>
     <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B229" t="inlineStr">
         <is>
           <t>Total</t>
@@ -3474,6 +4499,11 @@
       </c>
     </row>
     <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B231" t="inlineStr">
         <is>
           <t>Total</t>
@@ -3505,6 +4535,11 @@
       </c>
     </row>
     <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B233" t="inlineStr">
         <is>
           <t>Matamoros</t>
@@ -3518,6 +4553,11 @@
       </c>
     </row>
     <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B234" t="inlineStr">
         <is>
           <t>Tula</t>
@@ -3531,6 +4571,11 @@
       </c>
     </row>
     <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B235" t="inlineStr">
         <is>
           <t>Total</t>
@@ -3562,6 +4607,11 @@
       </c>
     </row>
     <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B237" t="inlineStr">
         <is>
           <t>Calpulalpan</t>
@@ -3575,6 +4625,11 @@
       </c>
     </row>
     <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B238" t="inlineStr">
         <is>
           <t>Chiautempan</t>
@@ -3588,6 +4643,11 @@
       </c>
     </row>
     <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B239" t="inlineStr">
         <is>
           <t>Cuaxomulco</t>
@@ -3601,6 +4661,11 @@
       </c>
     </row>
     <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B240" t="inlineStr">
         <is>
           <t>Hueyotlipan</t>
@@ -3614,9 +4679,14 @@
       </c>
     </row>
     <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Muñoz de Domingo Arenas</t>
+          <t>Muñoz De Domingo Arenas</t>
         </is>
       </c>
       <c r="C241">
@@ -3627,6 +4697,11 @@
       </c>
     </row>
     <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B242" t="inlineStr">
         <is>
           <t>Panotla</t>
@@ -3640,6 +4715,11 @@
       </c>
     </row>
     <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B243" t="inlineStr">
         <is>
           <t>San Lucas Tecopilco</t>
@@ -3653,6 +4733,11 @@
       </c>
     </row>
     <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B244" t="inlineStr">
         <is>
           <t>Tlaxcala</t>
@@ -3666,6 +4751,11 @@
       </c>
     </row>
     <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B245" t="inlineStr">
         <is>
           <t>Tlaxco</t>
@@ -3679,6 +4769,11 @@
       </c>
     </row>
     <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B246" t="inlineStr">
         <is>
           <t>Tzompantepec</t>
@@ -3692,6 +4787,11 @@
       </c>
     </row>
     <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B247" t="inlineStr">
         <is>
           <t>Xaltocan</t>
@@ -3705,6 +4805,11 @@
       </c>
     </row>
     <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B248" t="inlineStr">
         <is>
           <t>Yauhquemehcan</t>
@@ -3718,6 +4823,11 @@
       </c>
     </row>
     <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B249" t="inlineStr">
         <is>
           <t>Zacatelco</t>
@@ -3731,6 +4841,11 @@
       </c>
     </row>
     <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B250" t="inlineStr">
         <is>
           <t>Total</t>
@@ -3762,6 +4877,11 @@
       </c>
     </row>
     <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B252" t="inlineStr">
         <is>
           <t>Catemaco</t>
@@ -3775,6 +4895,11 @@
       </c>
     </row>
     <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B253" t="inlineStr">
         <is>
           <t>Coatepec</t>
@@ -3788,6 +4913,11 @@
       </c>
     </row>
     <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B254" t="inlineStr">
         <is>
           <t>Coscomatepec</t>
@@ -3801,6 +4931,11 @@
       </c>
     </row>
     <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B255" t="inlineStr">
         <is>
           <t>Huatusco</t>
@@ -3814,6 +4949,11 @@
       </c>
     </row>
     <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B256" t="inlineStr">
         <is>
           <t>Isla</t>
@@ -3827,6 +4967,11 @@
       </c>
     </row>
     <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B257" t="inlineStr">
         <is>
           <t>Jalacingo</t>
@@ -3840,6 +4985,11 @@
       </c>
     </row>
     <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B258" t="inlineStr">
         <is>
           <t>Mecayapan</t>
@@ -3853,6 +5003,11 @@
       </c>
     </row>
     <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B259" t="inlineStr">
         <is>
           <t>Minatitlán</t>
@@ -3866,6 +5021,11 @@
       </c>
     </row>
     <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B260" t="inlineStr">
         <is>
           <t>Playa Vicente</t>
@@ -3879,6 +5039,11 @@
       </c>
     </row>
     <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B261" t="inlineStr">
         <is>
           <t>Tierra Blanca</t>
@@ -3892,6 +5057,11 @@
       </c>
     </row>
     <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B262" t="inlineStr">
         <is>
           <t>Xalapa</t>
@@ -3905,6 +5075,11 @@
       </c>
     </row>
     <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B263" t="inlineStr">
         <is>
           <t>Total</t>
@@ -3936,6 +5111,11 @@
       </c>
     </row>
     <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B265" t="inlineStr">
         <is>
           <t>Atolinga</t>
@@ -3949,6 +5129,11 @@
       </c>
     </row>
     <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B266" t="inlineStr">
         <is>
           <t>Benito Juárez</t>
@@ -3962,6 +5147,11 @@
       </c>
     </row>
     <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B267" t="inlineStr">
         <is>
           <t>Fresnillo</t>
@@ -3975,6 +5165,11 @@
       </c>
     </row>
     <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B268" t="inlineStr">
         <is>
           <t>General Francisco R. Murguía</t>
@@ -3988,6 +5183,11 @@
       </c>
     </row>
     <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B269" t="inlineStr">
         <is>
           <t>Guadalupe</t>
@@ -4001,6 +5201,11 @@
       </c>
     </row>
     <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B270" t="inlineStr">
         <is>
           <t>Jalpa</t>
@@ -4014,6 +5219,11 @@
       </c>
     </row>
     <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B271" t="inlineStr">
         <is>
           <t>Juchipila</t>
@@ -4027,6 +5237,11 @@
       </c>
     </row>
     <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B272" t="inlineStr">
         <is>
           <t>Loreto</t>
@@ -4040,6 +5255,11 @@
       </c>
     </row>
     <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B273" t="inlineStr">
         <is>
           <t>Miguel Auza</t>
@@ -4053,6 +5273,11 @@
       </c>
     </row>
     <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B274" t="inlineStr">
         <is>
           <t>Tepetongo</t>
@@ -4066,9 +5291,14 @@
       </c>
     </row>
     <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Tlaltenango de Sánchez Román</t>
+          <t>Tlaltenango De Sánchez Román</t>
         </is>
       </c>
       <c r="C275">
@@ -4079,6 +5309,11 @@
       </c>
     </row>
     <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B276" t="inlineStr">
         <is>
           <t>Valparaíso</t>
@@ -4092,9 +5327,14 @@
       </c>
     </row>
     <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Villa de Cos</t>
+          <t>Villa De Cos</t>
         </is>
       </c>
       <c r="C277">
@@ -4105,6 +5345,11 @@
       </c>
     </row>
     <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B278" t="inlineStr">
         <is>
           <t>Villa González Ortega</t>
@@ -4118,6 +5363,11 @@
       </c>
     </row>
     <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B279" t="inlineStr">
         <is>
           <t>Villanueva</t>
@@ -4131,6 +5381,11 @@
       </c>
     </row>
     <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B280" t="inlineStr">
         <is>
           <t>Zacatecas</t>
@@ -4144,6 +5399,11 @@
       </c>
     </row>
     <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B281" t="inlineStr">
         <is>
           <t>Total</t>
@@ -4167,41 +5427,6 @@
       </c>
       <c r="D282">
         <v>1</v>
-      </c>
-    </row>
-    <row r="284">
-      <c r="A284" t="inlineStr">
-        <is>
-          <t>Tamaño de la muestra: 800,811</t>
-        </is>
-      </c>
-    </row>
-    <row r="285">
-      <c r="A285" t="inlineStr">
-        <is>
-          <t>Fuente: Expedición de Matrículas Consulares de Alta Seguridad en los Consulados de México en E.E.U.U.</t>
-        </is>
-      </c>
-    </row>
-    <row r="286">
-      <c r="A286" t="inlineStr">
-        <is>
-          <t>Elaborado por: Análisis de Información, Instituto de los Mexicanos en el Exterior</t>
-        </is>
-      </c>
-    </row>
-    <row r="287">
-      <c r="A287" t="inlineStr">
-        <is>
-          <t>Secretaría de Relaciones Exteriores</t>
-        </is>
-      </c>
-    </row>
-    <row r="288">
-      <c r="A288" t="inlineStr">
-        <is>
-          <t>Abril de 2020</t>
-        </is>
       </c>
     </row>
   </sheetData>
